--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/New folder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7B056C3-52E3-4F1E-9B2A-A6792B4610CF}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2169708A-4BF1-44F3-8A69-AF973512050D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{18415F18-79B1-4198-BB36-F5EFC947D5D7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>Custodian
 Item
@@ -184,6 +184,18 @@
   </si>
   <si>
     <t xml:space="preserve">Department : </t>
+  </si>
+  <si>
+    <t>Certified Correct by:</t>
+  </si>
+  <si>
+    <t>Signature over Printed Name</t>
+  </si>
+  <si>
+    <t>Custodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assistant to the Custodian</t>
   </si>
 </sst>
 </file>
@@ -193,7 +205,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -242,6 +254,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri  "/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri  "/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -257,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -317,12 +338,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -331,37 +370,56 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -677,8 +735,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89590D8-E0E3-4CF4-9912-0E99807A067D}">
-  <dimension ref="A2:AK8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:AK15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.44140625" style="2" customWidth="1"/>
@@ -718,85 +776,85 @@
     <col min="37" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:37" ht="15.6">
+      <c r="A2" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:37" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:37" ht="15.6">
+      <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:37">
+      <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="8" t="s">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="R6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="S6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="T6" s="3" t="s">
+      <c r="T6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="U6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="V6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="3" t="s">
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="AA6" s="4" t="s">
+      <c r="AA6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="AB6" s="4" t="s">
+      <c r="AB6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="AC6" s="4" t="s">
+      <c r="AC6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="AD6" s="6" t="s">
@@ -824,56 +882,56 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+    <row r="7" spans="1:37" ht="14.4" customHeight="1">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="3" t="s">
+      <c r="N7" s="8"/>
+      <c r="O7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="10"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="8" t="s">
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="X7" s="11" t="s">
+      <c r="X7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="Y7" s="8" t="s">
+      <c r="Y7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
       <c r="AD7" s="6"/>
       <c r="AE7" s="6"/>
       <c r="AF7" s="6"/>
@@ -883,44 +941,44 @@
       <c r="AJ7" s="6"/>
       <c r="AK7" s="6"/>
     </row>
-    <row r="8" spans="1:37" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="7" t="s">
+    <row r="8" spans="1:37" ht="43.2">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="7" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="4"/>
-      <c r="AB8" s="4"/>
-      <c r="AC8" s="4"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
       <c r="AF8" s="6"/>
@@ -930,8 +988,93 @@
       <c r="AJ8" s="6"/>
       <c r="AK8" s="6"/>
     </row>
+    <row r="11" spans="1:37">
+      <c r="B11" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="B14" s="16"/>
+      <c r="C14" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="I14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="B15" s="16"/>
+      <c r="C15" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="I15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="41">
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="T6:T8"/>
     <mergeCell ref="A6:A8"/>
@@ -948,27 +1091,6 @@
     <mergeCell ref="V6:V8"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="U6:U8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/New folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2169708A-4BF1-44F3-8A69-AF973512050D}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CA4426B-DD54-4221-8EC0-5CBBD0268071}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{18415F18-79B1-4198-BB36-F5EFC947D5D7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Custodian
 Item
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t xml:space="preserve">  Assistant to the Custodian</t>
+  </si>
+  <si>
+    <t>Verified by:</t>
   </si>
 </sst>
 </file>
@@ -264,7 +267,7 @@
       <name val="Calibri  "/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,7 +277,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="65"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -361,65 +370,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -436,6 +447,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -735,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89590D8-E0E3-4CF4-9912-0E99807A067D}">
-  <dimension ref="A2:AK15"/>
+  <dimension ref="A2:AK19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" style="2" bestFit="1" customWidth="1"/>
@@ -777,216 +792,216 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:37" ht="15.6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:37">
-      <c r="A3" s="1"/>
+      <c r="A3" s="3"/>
     </row>
     <row r="4" spans="1:37" ht="15.6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:37">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="9" t="s">
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="Q6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="R6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="S6" s="12" t="s">
+      <c r="S6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="U6" s="7" t="s">
+      <c r="U6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="V6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="W6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="7" t="s">
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AA6" s="8" t="s">
+      <c r="AA6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AB6" s="8" t="s">
+      <c r="AB6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="AC6" s="8" t="s">
+      <c r="AC6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AD6" s="6" t="s">
+      <c r="AD6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AE6" s="6" t="s">
+      <c r="AE6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="AF6" s="6" t="s">
+      <c r="AF6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="AG6" s="6" t="s">
+      <c r="AG6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="AH6" s="6" t="s">
+      <c r="AH6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AI6" s="6" t="s">
+      <c r="AI6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AJ6" s="6" t="s">
+      <c r="AJ6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AK6" s="6" t="s">
+      <c r="AK6" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="14.4" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="8"/>
-      <c r="O7" s="7" t="s">
+      <c r="N7" s="6"/>
+      <c r="O7" s="5" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="10"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="9" t="s">
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="X7" s="13" t="s">
+      <c r="X7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="Y7" s="9" t="s">
+      <c r="Y7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="6"/>
-      <c r="AK7" s="6"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+      <c r="AI7" s="9"/>
+      <c r="AJ7" s="9"/>
+      <c r="AK7" s="9"/>
     </row>
     <row r="8" spans="1:37" ht="43.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="3" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="11"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="13"/>
       <c r="X8" s="14"/>
-      <c r="Y8" s="11"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="6"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="9"/>
     </row>
     <row r="11" spans="1:37">
       <c r="B11" s="15" t="s">
@@ -997,7 +1012,9 @@
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="H11" s="15" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="12" spans="1:37">
       <c r="B12" s="15"/>
@@ -1016,26 +1033,26 @@
       <c r="F13" s="17"/>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" spans="1:37">
       <c r="B14" s="16"/>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="I14" s="20" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="I14" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
     </row>
     <row r="15" spans="1:37">
-      <c r="B15" s="16"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="21" t="s">
         <v>45</v>
       </c>
@@ -1047,6 +1064,18 @@
       </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="B16" s="22"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="22"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="22"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -1055,6 +1084,10 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="I15:K15"/>
     <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AJ6:AJ8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
@@ -1071,10 +1104,6 @@
     <mergeCell ref="AH6:AH8"/>
     <mergeCell ref="U6:U8"/>
     <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Y7:Y8"/>
     <mergeCell ref="AK6:AK8"/>
     <mergeCell ref="T6:T8"/>
     <mergeCell ref="A6:A8"/>

--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CA4426B-DD54-4221-8EC0-5CBBD0268071}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3869640D-DF07-4998-8DCE-A01346ADB562}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{18415F18-79B1-4198-BB36-F5EFC947D5D7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Custodian
 Item
@@ -45,15 +45,6 @@
 Number</t>
   </si>
   <si>
-    <t>Sub-Account</t>
-  </si>
-  <si>
-    <t>Article</t>
-  </si>
-  <si>
-    <t>Sub-Article</t>
-  </si>
-  <si>
     <t>DESCRIPTION</t>
   </si>
   <si>
@@ -180,9 +171,6 @@
     <t>ANNEX</t>
   </si>
   <si>
-    <t>AS OF</t>
-  </si>
-  <si>
     <t xml:space="preserve">Department : </t>
   </si>
   <si>
@@ -199,6 +187,9 @@
   </si>
   <si>
     <t>Verified by:</t>
+  </si>
+  <si>
+    <t>Sub-Account / Article</t>
   </si>
 </sst>
 </file>
@@ -267,7 +258,7 @@
       <name val="Calibri  "/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,14 +271,8 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="65"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -365,12 +350,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -379,58 +395,65 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -750,376 +773,344 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89590D8-E0E3-4CF4-9912-0E99807A067D}">
-  <dimension ref="A2:AK19"/>
+  <dimension ref="A2:AI16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.44140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="14.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.88671875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17" style="2" customWidth="1"/>
-    <col min="13" max="13" width="25" style="2" customWidth="1"/>
-    <col min="14" max="15" width="8.88671875" style="2"/>
-    <col min="16" max="16" width="18.44140625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="19.44140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="19.5546875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="21.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="14.21875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="18.5546875" style="2" customWidth="1"/>
-    <col min="22" max="22" width="15" style="2" customWidth="1"/>
-    <col min="23" max="23" width="20.109375" style="2" customWidth="1"/>
-    <col min="24" max="24" width="15.6640625" style="2" customWidth="1"/>
-    <col min="25" max="25" width="17.21875" style="2" customWidth="1"/>
-    <col min="26" max="26" width="27.77734375" style="2" customWidth="1"/>
-    <col min="27" max="27" width="16.6640625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="17.88671875" style="2" customWidth="1"/>
-    <col min="29" max="29" width="19.44140625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="17.5546875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="15.6640625" style="2" customWidth="1"/>
-    <col min="32" max="32" width="20.88671875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="16.88671875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="22.6640625" style="2" customWidth="1"/>
-    <col min="35" max="35" width="16.44140625" style="2" customWidth="1"/>
-    <col min="36" max="36" width="12.6640625" style="2" customWidth="1"/>
-    <col min="37" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="41.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="29.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25" style="2" customWidth="1"/>
+    <col min="12" max="13" width="8.88671875" style="2"/>
+    <col min="14" max="14" width="18.44140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="19.44140625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="19.5546875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="21.21875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="18.5546875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="15" style="2" customWidth="1"/>
+    <col min="21" max="21" width="20.109375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="15.6640625" style="2" customWidth="1"/>
+    <col min="23" max="23" width="17.21875" style="2" customWidth="1"/>
+    <col min="24" max="24" width="27.77734375" style="2" customWidth="1"/>
+    <col min="25" max="25" width="16.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="17.88671875" style="2" customWidth="1"/>
+    <col min="27" max="27" width="19.44140625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="17.5546875" style="2" customWidth="1"/>
+    <col min="29" max="29" width="15.6640625" style="2" customWidth="1"/>
+    <col min="30" max="30" width="20.88671875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="16.88671875" style="2" customWidth="1"/>
+    <col min="32" max="32" width="22.6640625" style="2" customWidth="1"/>
+    <col min="33" max="33" width="16.44140625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" style="2" customWidth="1"/>
+    <col min="35" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:37" ht="15.6">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:35" ht="15.6">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:35">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:35" ht="15.6">
+      <c r="A4" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35">
+      <c r="A6" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+      <c r="X6" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI6" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" ht="14.4" customHeight="1">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="16"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="V7" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="W7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="12"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+    </row>
+    <row r="8" spans="1:35" ht="43.2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="14"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="14"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+    </row>
+    <row r="9" spans="1:35">
+      <c r="E9" s="8"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="1:35">
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="12" spans="1:35">
+      <c r="B12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="G12" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
+      <c r="B13" s="10"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:35">
+      <c r="B14" s="5"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="5"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:35">
+      <c r="B15" s="5"/>
+      <c r="C15" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="H15" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="25"/>
+    </row>
+    <row r="16" spans="1:35">
+      <c r="B16" s="5"/>
+      <c r="C16" s="19" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:37">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" spans="1:37" ht="15.6">
-      <c r="A4" s="4" t="s">
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="H16" s="19" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:37">
-      <c r="A6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="W6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="AK6" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" ht="14.4" customHeight="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="X7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="9"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
-      <c r="AJ7" s="9"/>
-      <c r="AK7" s="9"/>
-    </row>
-    <row r="8" spans="1:37" ht="43.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" s="5"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="9"/>
-      <c r="AE8" s="9"/>
-      <c r="AF8" s="9"/>
-      <c r="AG8" s="9"/>
-      <c r="AH8" s="9"/>
-      <c r="AI8" s="9"/>
-      <c r="AJ8" s="9"/>
-      <c r="AK8" s="9"/>
-    </row>
-    <row r="11" spans="1:37">
-      <c r="B11" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37">
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-    </row>
-    <row r="13" spans="1:37">
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="B14" s="16"/>
-      <c r="C14" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="I14" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="I15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="B16" s="22"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="22"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="22"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="22"/>
+      <c r="I16" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="AI6:AI8"/>
+  <mergeCells count="39">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="AA6:AA8"/>
     <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="R6:R8"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:C7"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="O6:O8"/>
     <mergeCell ref="P6:P8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="H6:O6"/>
     <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="V6:V8"/>
-    <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3869640D-DF07-4998-8DCE-A01346ADB562}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07FF07B8-393B-45AA-A2C5-327FE1F3C338}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{18415F18-79B1-4198-BB36-F5EFC947D5D7}"/>
   </bookViews>
@@ -199,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +257,12 @@
       <color theme="1"/>
       <name val="Calibri  "/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -386,7 +392,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -400,41 +406,31 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -453,6 +449,27 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -819,70 +836,70 @@
       <c r="A3" s="3"/>
     </row>
     <row r="4" spans="1:35" ht="15.6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:35">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="15" t="s">
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="Q6" s="18" t="s">
+      <c r="Q6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="13" t="s">
+      <c r="R6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="T6" s="13" t="s">
+      <c r="T6" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="U6" s="14" t="s">
+      <c r="U6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="14"/>
-      <c r="W6" s="14"/>
-      <c r="X6" s="13" t="s">
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="Y6" s="14" t="s">
+      <c r="Y6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Z6" s="14" t="s">
+      <c r="Z6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AA6" s="14" t="s">
+      <c r="AA6" s="13" t="s">
         <v>12</v>
       </c>
       <c r="AB6" s="12" t="s">
@@ -911,53 +928,53 @@
       </c>
     </row>
     <row r="7" spans="1:35" ht="14.4" customHeight="1">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="14" t="s">
+      <c r="A7" s="22"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="13" t="s">
+      <c r="L7" s="13"/>
+      <c r="M7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="16"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="15" t="s">
+      <c r="N7" s="23"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="V7" s="20" t="s">
+      <c r="V7" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="W7" s="15" t="s">
+      <c r="W7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
       <c r="AB7" s="12"/>
       <c r="AC7" s="12"/>
       <c r="AD7" s="12"/>
@@ -968,41 +985,41 @@
       <c r="AI7" s="12"/>
     </row>
     <row r="8" spans="1:35" ht="43.2">
-      <c r="A8" s="13"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
       <c r="K8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="13"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="21"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
       <c r="AB8" s="12"/>
       <c r="AC8" s="12"/>
       <c r="AD8" s="12"/>
@@ -1013,25 +1030,129 @@
       <c r="AI8" s="12"/>
     </row>
     <row r="9" spans="1:35">
-      <c r="E9" s="8"/>
-      <c r="Q9" s="7"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="27"/>
+      <c r="AC9" s="27"/>
+      <c r="AD9" s="27"/>
+      <c r="AE9" s="27"/>
+      <c r="AF9" s="27"/>
+      <c r="AG9" s="27"/>
+      <c r="AH9" s="27"/>
+      <c r="AI9" s="27"/>
     </row>
     <row r="10" spans="1:35">
-      <c r="Q10" s="7"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="25"/>
+      <c r="AI10" s="25"/>
+    </row>
+    <row r="11" spans="1:35">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
+      <c r="AA11" s="10"/>
+      <c r="AB11" s="10"/>
+      <c r="AC11" s="10"/>
+      <c r="AD11" s="10"/>
+      <c r="AE11" s="10"/>
+      <c r="AF11" s="10"/>
+      <c r="AG11" s="10"/>
+      <c r="AH11" s="10"/>
+      <c r="AI11" s="10"/>
     </row>
     <row r="12" spans="1:35">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:35">
-      <c r="B13" s="10"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1039,39 +1160,62 @@
     </row>
     <row r="14" spans="1:35">
       <c r="B14" s="5"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="5"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:35">
       <c r="B15" s="5"/>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="H15" s="25" t="s">
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="H15" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="25"/>
+      <c r="I15" s="21"/>
     </row>
     <row r="16" spans="1:35">
       <c r="B16" s="5"/>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="H16" s="19" t="s">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="H16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="19"/>
+      <c r="I16" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="F6:M6"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:M8"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="AG6:AG8"/>
     <mergeCell ref="Z6:Z8"/>
@@ -1088,29 +1232,6 @@
     <mergeCell ref="AA6:AA8"/>
     <mergeCell ref="AB6:AB8"/>
     <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="F6:M6"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Templates New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07FF07B8-393B-45AA-A2C5-327FE1F3C338}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{7ACEABFC-0307-4110-9247-504CA29F57D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEA603FC-1CA4-4732-BE22-68EDFDB793D2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{18415F18-79B1-4198-BB36-F5EFC947D5D7}"/>
   </bookViews>
@@ -278,7 +278,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -387,12 +387,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -415,22 +426,37 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -450,25 +476,31 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -790,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89590D8-E0E3-4CF4-9912-0E99807A067D}">
-  <dimension ref="A2:AI16"/>
+  <dimension ref="A2:AI17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" style="2" bestFit="1" customWidth="1"/>
@@ -841,358 +873,418 @@
       </c>
     </row>
     <row r="6" spans="1:35">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="14" t="s">
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="O6" s="22" t="s">
+      <c r="O6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="22" t="s">
+      <c r="P6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="Q6" s="24" t="s">
+      <c r="Q6" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="22" t="s">
+      <c r="R6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="S6" s="22" t="s">
+      <c r="S6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="T6" s="22" t="s">
+      <c r="T6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="U6" s="13" t="s">
+      <c r="U6" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="22" t="s">
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Y6" s="13" t="s">
+      <c r="Y6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="Z6" s="13" t="s">
+      <c r="Z6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="AA6" s="13" t="s">
+      <c r="AA6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AB6" s="12" t="s">
+      <c r="AB6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="AC6" s="12" t="s">
+      <c r="AC6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="AD6" s="12" t="s">
+      <c r="AD6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AE6" s="12" t="s">
+      <c r="AE6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="AF6" s="12" t="s">
+      <c r="AF6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AG6" s="12" t="s">
+      <c r="AG6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="AH6" s="12" t="s">
+      <c r="AH6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AI6" s="12" t="s">
+      <c r="AI6" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="14.4" customHeight="1">
-      <c r="A7" s="22"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="13" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="22" t="s">
+      <c r="L7" s="15"/>
+      <c r="M7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="14" t="s">
+      <c r="N7" s="17"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="V7" s="16" t="s">
+      <c r="V7" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="W7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="12"/>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="12"/>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="12"/>
+      <c r="X7" s="14"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="13"/>
+      <c r="AI7" s="13"/>
     </row>
     <row r="8" spans="1:35" ht="43.2">
-      <c r="A8" s="22"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
       <c r="K8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="22"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-    </row>
-    <row r="9" spans="1:35">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27"/>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27"/>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="14"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AH8" s="13"/>
+      <c r="AI8" s="13"/>
+    </row>
+    <row r="9" spans="1:35" ht="0.6" hidden="1" customHeight="1">
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="27"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="32"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="32"/>
+      <c r="AI9" s="32"/>
     </row>
     <row r="10" spans="1:35">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="25"/>
-      <c r="AI10" s="25"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="33"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="35"/>
     </row>
     <row r="11" spans="1:35">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
-      <c r="AB11" s="10"/>
-      <c r="AC11" s="10"/>
-      <c r="AD11" s="10"/>
-      <c r="AE11" s="10"/>
-      <c r="AF11" s="10"/>
-      <c r="AG11" s="10"/>
-      <c r="AH11" s="10"/>
-      <c r="AI11" s="10"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="11"/>
+      <c r="AI11" s="11"/>
     </row>
     <row r="12" spans="1:35">
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+    </row>
+    <row r="13" spans="1:35">
+      <c r="B13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="G12" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35">
-      <c r="B13" s="8"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="G13" s="8" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="14" spans="1:35">
-      <c r="B14" s="5"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:35">
       <c r="B15" s="5"/>
-      <c r="C15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="H15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="21"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="5"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:35">
       <c r="B16" s="5"/>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="H16" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="26"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="5"/>
+      <c r="C17" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="H16" s="11" t="s">
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="H17" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="11"/>
+      <c r="I17" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:M8"/>
     <mergeCell ref="AI6:AI8"/>
     <mergeCell ref="R6:R8"/>
     <mergeCell ref="A6:A8"/>
@@ -1209,29 +1301,6 @@
     <mergeCell ref="AH6:AH8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_14/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_22/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{BB777957-C5AF-45A9-AA39-59C1EB44883A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C298E6A6-974D-4398-A7EE-6611A3B8A3E0}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{BB777957-C5AF-45A9-AA39-59C1EB44883A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{844C4108-23F2-4367-ACB8-60D647298986}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Custodian 
 Item 
@@ -75,11 +75,6 @@
     <t>Other Particulars</t>
   </si>
   <si>
-    <t>(Type / Specifications / Generic Name / 
-Volume / Dosage Strength / Dosage Form / 
-Other Descriptions)</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -101,12 +96,6 @@
   <si>
     <t>Property 
 Number</t>
-  </si>
-  <si>
-    <t>Old
-Amounts
-(recorded 
-in RPCPPE)</t>
   </si>
   <si>
     <t>P.O. 
@@ -198,21 +187,6 @@
 Number</t>
   </si>
   <si>
-    <t>Certified Correct by:</t>
-  </si>
-  <si>
-    <t>Signature over Printed Name</t>
-  </si>
-  <si>
-    <t>Custodian</t>
-  </si>
-  <si>
-    <t>Verified by:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Assistant to the Custodian</t>
-  </si>
-  <si>
     <t>Department:</t>
   </si>
   <si>
@@ -220,13 +194,25 @@
   </si>
   <si>
     <t>REPORT ON THE PHYSICAL COUNT OF EQUIPMENT</t>
+  </si>
+  <si>
+    <t>Old
+Amounts
+(in RPCPPE)</t>
+  </si>
+  <si>
+    <t>Specifications</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,10 +261,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri  "/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,12 +278,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
@@ -397,18 +380,13 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -418,37 +396,13 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -456,17 +410,63 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="hair">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -474,9 +474,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -487,66 +484,91 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -863,438 +885,365 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8360D46A-3DF6-4255-A30F-B9008CB83C98}">
-  <dimension ref="B2:AN19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="B2:AN15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="8.88671875" style="3"/>
-    <col min="10" max="10" width="23.33203125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="8.88671875" style="3"/>
-    <col min="12" max="12" width="37.33203125" style="3" customWidth="1"/>
-    <col min="13" max="16" width="8.88671875" style="3"/>
-    <col min="17" max="17" width="10.21875" style="3" customWidth="1"/>
-    <col min="18" max="20" width="8.88671875" style="3"/>
-    <col min="21" max="21" width="19.5546875" style="3" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" style="3" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" style="3" customWidth="1"/>
-    <col min="24" max="27" width="8.88671875" style="3"/>
-    <col min="28" max="28" width="11.5546875" style="3" customWidth="1"/>
-    <col min="29" max="33" width="8.88671875" style="3"/>
-    <col min="34" max="34" width="12.77734375" style="3" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" style="3"/>
-    <col min="36" max="36" width="18.109375" style="3" customWidth="1"/>
-    <col min="37" max="16384" width="8.88671875" style="3"/>
+    <col min="5" max="5" width="8.88671875" style="3"/>
+    <col min="6" max="6" width="28.44140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="3"/>
+    <col min="8" max="8" width="11.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="28" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="42.33203125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" style="32"/>
+    <col min="14" max="14" width="8.88671875" style="3"/>
+    <col min="15" max="16" width="16.5546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.21875" style="28" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="3"/>
+    <col min="21" max="21" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" style="28" customWidth="1"/>
+    <col min="23" max="23" width="20.33203125" style="28" customWidth="1"/>
+    <col min="24" max="24" width="11.21875" style="28" customWidth="1"/>
+    <col min="25" max="25" width="10.77734375" style="3" customWidth="1"/>
+    <col min="26" max="27" width="8.88671875" style="3"/>
+    <col min="28" max="28" width="11.5546875" style="28" customWidth="1"/>
+    <col min="29" max="29" width="12.44140625" style="3" customWidth="1"/>
+    <col min="30" max="32" width="8.88671875" style="3"/>
+    <col min="33" max="33" width="22.88671875" style="3" customWidth="1"/>
+    <col min="34" max="34" width="25.21875" style="3" customWidth="1"/>
+    <col min="35" max="35" width="25.33203125" style="3" customWidth="1"/>
+    <col min="36" max="36" width="26.33203125" style="3" customWidth="1"/>
+    <col min="37" max="37" width="6.5546875" style="3" customWidth="1"/>
+    <col min="38" max="38" width="17.77734375" style="3" customWidth="1"/>
+    <col min="39" max="39" width="18" style="3" customWidth="1"/>
+    <col min="40" max="40" width="6.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:40" s="1" customFormat="1" ht="15.6">
-      <c r="B2" s="8"/>
+    <row r="2" spans="2:40" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="7"/>
+      <c r="M2" s="30"/>
+      <c r="Q2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="AB2" s="26"/>
     </row>
-    <row r="3" spans="2:40" s="2" customFormat="1" ht="18">
-      <c r="B3" s="9" t="s">
-        <v>49</v>
-      </c>
+    <row r="3" spans="2:40" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="B3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="31"/>
+      <c r="Q3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="AB3" s="27"/>
     </row>
-    <row r="4" spans="2:40" ht="15.6">
+    <row r="4" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="2:40" ht="15.6">
+    <row r="5" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="2:40" ht="15.6">
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="13"/>
+    <row r="6" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="2:40" ht="15" thickBot="1"/>
-    <row r="8" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1">
-      <c r="B8" s="25" t="s">
+    <row r="7" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="9"/>
+    </row>
+    <row r="9" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="1"/>
+      <c r="C9" s="9"/>
+    </row>
+    <row r="10" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="1"/>
+      <c r="C10" s="9"/>
+    </row>
+    <row r="11" spans="2:40" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C12" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="21" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="21" t="s">
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="21" t="s">
+      <c r="Q12" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="R12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="21" t="s">
+      <c r="U12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="V12" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="R8" s="21" t="s">
+      <c r="W12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="X12" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z12" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA12" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB12" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="S8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="U8" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="V8" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="W8" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="X8" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y8" s="21" t="s">
+      <c r="AF12" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH12" s="13"/>
+      <c r="AI12" s="13"/>
+      <c r="AJ12" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK12" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL12" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM12" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN12" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Z8" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA8" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB8" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC8" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD8" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE8" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF8" s="21" t="s">
+    </row>
+    <row r="13" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="21"/>
+      <c r="C13" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="15"/>
+      <c r="AD13" s="15"/>
+      <c r="AE13" s="15"/>
+      <c r="AF13" s="15"/>
+      <c r="AG13" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="AG8" s="16" t="s">
+      <c r="AH13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="AK8" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL8" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM8" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="AN8" s="16" t="s">
-        <v>48</v>
-      </c>
+      <c r="AI13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ13" s="15"/>
+      <c r="AK13" s="15"/>
+      <c r="AL13" s="15"/>
+      <c r="AM13" s="24"/>
+      <c r="AN13" s="15"/>
     </row>
-    <row r="9" spans="2:40" s="4" customFormat="1">
-      <c r="B9" s="26"/>
-      <c r="C9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI9" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ9" s="17"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="17"/>
-      <c r="AM9" s="23"/>
-      <c r="AN9" s="17"/>
+    <row r="14" spans="2:40" s="4" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="22"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="12"/>
+      <c r="AA14" s="12"/>
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="12"/>
+      <c r="AD14" s="12"/>
+      <c r="AE14" s="12"/>
+      <c r="AF14" s="12"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="12"/>
+      <c r="AI14" s="12"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="25"/>
+      <c r="AN14" s="12"/>
     </row>
-    <row r="10" spans="2:40" s="4" customFormat="1" ht="43.8" thickBot="1">
-      <c r="B10" s="27"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="18"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="18"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="18"/>
-      <c r="AE10" s="18"/>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="18"/>
-      <c r="AH10" s="18"/>
-      <c r="AI10" s="18"/>
-      <c r="AJ10" s="18"/>
-      <c r="AK10" s="18"/>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="24"/>
-      <c r="AN10" s="18"/>
-    </row>
-    <row r="11" spans="2:40" s="4" customFormat="1" ht="0.6" customHeight="1">
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
-      <c r="AG11" s="14"/>
-      <c r="AH11" s="14"/>
-      <c r="AI11" s="14"/>
-      <c r="AJ11" s="14"/>
-      <c r="AK11" s="14"/>
-      <c r="AL11" s="14"/>
-      <c r="AM11" s="14"/>
-      <c r="AN11" s="14"/>
-    </row>
-    <row r="12" spans="2:40">
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="30"/>
-      <c r="AK12" s="30"/>
-      <c r="AL12" s="30"/>
-      <c r="AM12" s="30"/>
-      <c r="AN12" s="30"/>
-    </row>
-    <row r="15" spans="2:40">
-      <c r="C15" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-    </row>
-    <row r="16" spans="2:40">
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="4:12">
-      <c r="J17" s="11"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-    </row>
-    <row r="18" spans="4:12">
-      <c r="D18" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="28"/>
-    </row>
-    <row r="19" spans="4:12">
-      <c r="D19" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="L19" s="29"/>
+    <row r="15" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="34"/>
+      <c r="Q15" s="38"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="29"/>
+      <c r="AB15" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="AG8:AI8"/>
-    <mergeCell ref="AG9:AG10"/>
-    <mergeCell ref="AL8:AL10"/>
-    <mergeCell ref="R8:R10"/>
-    <mergeCell ref="AC8:AC10"/>
-    <mergeCell ref="AD8:AD10"/>
-    <mergeCell ref="AE8:AE10"/>
-    <mergeCell ref="AF8:AF10"/>
-    <mergeCell ref="AA8:AA10"/>
-    <mergeCell ref="AB8:AB10"/>
-    <mergeCell ref="U8:U10"/>
-    <mergeCell ref="V8:V10"/>
-    <mergeCell ref="W8:W10"/>
-    <mergeCell ref="X8:X10"/>
-    <mergeCell ref="AK8:AK10"/>
-    <mergeCell ref="AH9:AH10"/>
-    <mergeCell ref="AI9:AI10"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="AN8:AN10"/>
-    <mergeCell ref="G8:N8"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="Y8:Y10"/>
-    <mergeCell ref="Z8:Z10"/>
-    <mergeCell ref="S8:S10"/>
-    <mergeCell ref="T8:T10"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="AM8:AM10"/>
-    <mergeCell ref="AJ8:AJ10"/>
-    <mergeCell ref="O8:O10"/>
+  <mergeCells count="40">
+    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="G12:N12"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="S12:S14"/>
+    <mergeCell ref="T12:T14"/>
+    <mergeCell ref="Q12:Q14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="O12:O14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AH13:AH14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AD12:AD14"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="AF12:AF14"/>
+    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="U12:U14"/>
+    <mergeCell ref="V12:V14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="X12:X14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1302,12 +1251,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1461,15 +1407,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1493,17 +1450,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_03_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_04_08/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{BB777957-C5AF-45A9-AA39-59C1EB44883A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{844C4108-23F2-4367-ACB8-60D647298986}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{BB777957-C5AF-45A9-AA39-59C1EB44883A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E66F509-215E-42A6-B7E8-406C4D3C02F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -154,12 +154,6 @@
 Location</t>
   </si>
   <si>
-    <t>PAR / ARE / MR</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
     <t>Accountable 
 Officer</t>
   </si>
@@ -202,6 +196,12 @@
   </si>
   <si>
     <t>Specifications</t>
+  </si>
+  <si>
+    <t>PAR / ICS / ARE / MR / RPCPPE</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -210,7 +210,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -488,82 +488,82 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,10 +582,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -900,19 +896,19 @@
     <col min="10" max="10" width="28" style="3" customWidth="1"/>
     <col min="11" max="11" width="10.33203125" style="3" customWidth="1"/>
     <col min="12" max="12" width="42.33203125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" style="32"/>
+    <col min="13" max="13" width="8.88671875" style="17"/>
     <col min="14" max="14" width="8.88671875" style="3"/>
     <col min="15" max="16" width="16.5546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="10.21875" style="28" customWidth="1"/>
+    <col min="17" max="17" width="10.21875" style="13" customWidth="1"/>
     <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
     <col min="19" max="20" width="8.88671875" style="3"/>
     <col min="21" max="21" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" style="28" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" style="28" customWidth="1"/>
-    <col min="24" max="24" width="11.21875" style="28" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" style="13" customWidth="1"/>
+    <col min="23" max="23" width="20.33203125" style="13" customWidth="1"/>
+    <col min="24" max="24" width="11.21875" style="13" customWidth="1"/>
     <col min="25" max="25" width="10.77734375" style="3" customWidth="1"/>
     <col min="26" max="27" width="8.88671875" style="3"/>
-    <col min="28" max="28" width="11.5546875" style="28" customWidth="1"/>
+    <col min="28" max="28" width="11.5546875" style="13" customWidth="1"/>
     <col min="29" max="29" width="12.44140625" style="3" customWidth="1"/>
     <col min="30" max="32" width="8.88671875" style="3"/>
     <col min="33" max="33" width="22.88671875" style="3" customWidth="1"/>
@@ -928,23 +924,23 @@
   <sheetData>
     <row r="2" spans="2:40" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
-      <c r="M2" s="30"/>
-      <c r="Q2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="AB2" s="26"/>
+      <c r="M2" s="15"/>
+      <c r="Q2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="AB2" s="11"/>
     </row>
     <row r="3" spans="2:40" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="31"/>
-      <c r="Q3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="AB3" s="27"/>
+        <v>40</v>
+      </c>
+      <c r="M3" s="16"/>
+      <c r="Q3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="AB3" s="12"/>
     </row>
     <row r="4" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
@@ -966,7 +962,7 @@
     </row>
     <row r="8" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="9"/>
     </row>
@@ -980,213 +976,213 @@
     </row>
     <row r="11" spans="2:40" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="12" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="21"/>
+      <c r="E12" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="14" t="s">
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="14" t="s">
+      <c r="P12" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="Q12" s="35" t="s">
+      <c r="Q12" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="R12" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="U12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="V12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="W12" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="X12" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y12" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z12" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA12" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB12" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC12" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD12" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="R12" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="S12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="U12" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="V12" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="W12" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="X12" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y12" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z12" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA12" s="14" t="s">
+      <c r="AH12" s="21"/>
+      <c r="AI12" s="21"/>
+      <c r="AJ12" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK12" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN12" s="21" t="s">
         <v>39</v>
-      </c>
-      <c r="AB12" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC12" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD12" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG12" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK12" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM12" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN12" s="13" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="13" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="32"/>
+      <c r="C13" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L13" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="36"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
-      <c r="AE13" s="15"/>
-      <c r="AF13" s="15"/>
-      <c r="AG13" s="15" t="s">
+      <c r="M13" s="36"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="26"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH13" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI13" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="AH13" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI13" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ13" s="15"/>
-      <c r="AK13" s="15"/>
-      <c r="AL13" s="15"/>
-      <c r="AM13" s="24"/>
-      <c r="AN13" s="15"/>
+      <c r="AJ13" s="22"/>
+      <c r="AK13" s="22"/>
+      <c r="AL13" s="22"/>
+      <c r="AM13" s="39"/>
+      <c r="AN13" s="22"/>
     </row>
     <row r="14" spans="2:40" s="4" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="22"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
       <c r="L14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="M14" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="18" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="37"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="12"/>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="12"/>
-      <c r="AK14" s="12"/>
-      <c r="AL14" s="12"/>
-      <c r="AM14" s="25"/>
-      <c r="AN14" s="12"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="23"/>
+      <c r="AJ14" s="23"/>
+      <c r="AK14" s="23"/>
+      <c r="AL14" s="23"/>
+      <c r="AM14" s="40"/>
+      <c r="AN14" s="23"/>
     </row>
     <row r="15" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="10"/>
@@ -1194,16 +1190,20 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="34"/>
-      <c r="Q15" s="38"/>
+      <c r="M15" s="19"/>
+      <c r="Q15" s="20"/>
       <c r="U15" s="10"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="29"/>
-      <c r="AB15" s="29"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="14"/>
+      <c r="AB15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="O12:O14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="P12:P14"/>
+    <mergeCell ref="L13:N13"/>
     <mergeCell ref="AN12:AN14"/>
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G13:G14"/>
@@ -1218,20 +1218,12 @@
     <mergeCell ref="Q12:Q14"/>
     <mergeCell ref="AM12:AM14"/>
     <mergeCell ref="AJ12:AJ14"/>
-    <mergeCell ref="O12:O14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AK12:AK14"/>
-    <mergeCell ref="AH13:AH14"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="F12:F14"/>
     <mergeCell ref="C13:C14"/>
-    <mergeCell ref="AI13:AI14"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="P12:P14"/>
-    <mergeCell ref="L13:N13"/>
     <mergeCell ref="AL12:AL14"/>
     <mergeCell ref="R12:R14"/>
     <mergeCell ref="AC12:AC14"/>
@@ -1244,6 +1236,10 @@
     <mergeCell ref="V12:V14"/>
     <mergeCell ref="W12:W14"/>
     <mergeCell ref="X12:X14"/>
+    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AH13:AH14"/>
+    <mergeCell ref="AI13:AI14"/>
+    <mergeCell ref="AG12:AI12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -5,16 +5,161 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template 2025_04_08/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{BB777957-C5AF-45A9-AA39-59C1EB44883A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E66F509-215E-42A6-B7E8-406C4D3C02F1}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{148159D7-4E6E-4289-9B74-FEF0EA63799C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="832" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="a">#REF!</definedName>
+    <definedName name="Account">#REF!</definedName>
+    <definedName name="Account1">#REF!</definedName>
+    <definedName name="Account2">#REF!</definedName>
+    <definedName name="Account3">#REF!</definedName>
+    <definedName name="AirconditioningUnits">#REF!</definedName>
+    <definedName name="Banca">#REF!</definedName>
+    <definedName name="Books">#REF!</definedName>
+    <definedName name="BuildingComponents">#REF!</definedName>
+    <definedName name="Buildings">#REF!</definedName>
+    <definedName name="Bulldozer">#REF!</definedName>
+    <definedName name="Calendar10Month">#REF!</definedName>
+    <definedName name="Calendar10MonthOption">MATCH(Calendar10Month,Months,0)</definedName>
+    <definedName name="Calendar10Year">#REF!</definedName>
+    <definedName name="Calendar11Month">#REF!</definedName>
+    <definedName name="Calendar11MonthOption">MATCH(Calendar11Month,Months,0)</definedName>
+    <definedName name="Calendar11Year">#REF!</definedName>
+    <definedName name="Calendar12Month">#REF!</definedName>
+    <definedName name="Calendar12MonthOption">MATCH(Calendar12Month,Months,0)</definedName>
+    <definedName name="Calendar12Year">#REF!</definedName>
+    <definedName name="Calendar1Month">#REF!</definedName>
+    <definedName name="Calendar1MonthOption">MATCH(Calendar1Month,Months,0)</definedName>
+    <definedName name="Calendar1Year">#REF!</definedName>
+    <definedName name="Calendar2Month">#REF!</definedName>
+    <definedName name="Calendar2MonthOption">MATCH(Calendar2Month,Months,0)</definedName>
+    <definedName name="Calendar2Year">#REF!</definedName>
+    <definedName name="Calendar3Month">#REF!</definedName>
+    <definedName name="Calendar3MonthOption">MATCH(Calendar3Month,Months,0)</definedName>
+    <definedName name="Calendar3Year">#REF!</definedName>
+    <definedName name="Calendar4Month">#REF!</definedName>
+    <definedName name="Calendar4MonthOption">MATCH(Calendar4Month,Months,0)</definedName>
+    <definedName name="Calendar4Year">#REF!</definedName>
+    <definedName name="Calendar5Month">#REF!</definedName>
+    <definedName name="Calendar5MonthOption">MATCH(Calendar5Month,Months,0)</definedName>
+    <definedName name="Calendar5Year">#REF!</definedName>
+    <definedName name="Calendar6Month">#REF!</definedName>
+    <definedName name="Calendar6MonthOption">MATCH(Calendar6Month,Months,0)</definedName>
+    <definedName name="Calendar6Year">#REF!</definedName>
+    <definedName name="Calendar7Month">#REF!</definedName>
+    <definedName name="Calendar7MonthOption">MATCH(Calendar7Month,Months,0)</definedName>
+    <definedName name="Calendar7Year">#REF!</definedName>
+    <definedName name="Calendar8Month">#REF!</definedName>
+    <definedName name="Calendar8MonthOption">MATCH(Calendar8Month,Months,0)</definedName>
+    <definedName name="Calendar8Year">#REF!</definedName>
+    <definedName name="Calendar9Month">#REF!</definedName>
+    <definedName name="Calendar9MonthOption">MATCH(Calendar9Month,Months,0)</definedName>
+    <definedName name="Calendar9Year">#REF!</definedName>
+    <definedName name="Car">#REF!</definedName>
+    <definedName name="ClosedCircuitTelevision">#REF!</definedName>
+    <definedName name="CommunicationEquipment">#REF!</definedName>
+    <definedName name="CommunicationsNetwork">#REF!</definedName>
+    <definedName name="Compactor">#REF!</definedName>
+    <definedName name="ComputerDesktopSet">#REF!</definedName>
+    <definedName name="Condition">#REF!</definedName>
+    <definedName name="Condition1">#REF!</definedName>
+    <definedName name="Condition2">#REF!</definedName>
+    <definedName name="Condition3">#REF!</definedName>
+    <definedName name="ConstructionandHeavyEquipment">#REF!</definedName>
+    <definedName name="DataCommunicationsEquipment">#REF!</definedName>
+    <definedName name="Days">{0,1,2,3,4,5,6}</definedName>
+    <definedName name="DiagnosticEquipment">#REF!</definedName>
+    <definedName name="DisasterResponseandRescue">#REF!</definedName>
+    <definedName name="Drones">#REF!</definedName>
+    <definedName name="Dropside">#REF!</definedName>
+    <definedName name="DumpTruck">#REF!</definedName>
+    <definedName name="Duplicating\PhotocopyingMachines">#REF!</definedName>
+    <definedName name="EarthquakeRescueEquipment">#REF!</definedName>
+    <definedName name="FirefightingEquipmentandAccessories">#REF!</definedName>
+    <definedName name="FloodControlSystems">#REF!</definedName>
+    <definedName name="FloodRescueEquipment">#REF!</definedName>
+    <definedName name="Forklift">#REF!</definedName>
+    <definedName name="Furniture\Fixtures\Books">#REF!</definedName>
+    <definedName name="FurnitureandFixtures">#REF!</definedName>
+    <definedName name="Guns">#REF!</definedName>
+    <definedName name="HighwaysandBridges">#REF!</definedName>
+    <definedName name="HospitalandHealthCenters">#REF!</definedName>
+    <definedName name="HospitalBeds">#REF!</definedName>
+    <definedName name="InformationandCommunicationTechnology">#REF!</definedName>
+    <definedName name="IrrigationCanalsandLaterals">#REF!</definedName>
+    <definedName name="LandslideRescueEquipment">#REF!</definedName>
+    <definedName name="Laptop">#REF!</definedName>
+    <definedName name="LifeSupport">#REF!</definedName>
+    <definedName name="Markets">#REF!</definedName>
+    <definedName name="MedicalEquipment">#REF!</definedName>
+    <definedName name="MedicalFurniture">#REF!</definedName>
+    <definedName name="MedicineTrolleys">#REF!</definedName>
+    <definedName name="MobileCar">#REF!</definedName>
+    <definedName name="MobileClinic">#REF!</definedName>
+    <definedName name="ModeofAcquisition">#REF!</definedName>
+    <definedName name="ModeofAcquisition1">#REF!</definedName>
+    <definedName name="Monitors">#REF!</definedName>
+    <definedName name="Months">{"January","February","March","April","May","June","July","August","September","October","November","December"}</definedName>
+    <definedName name="Motorboat">#REF!</definedName>
+    <definedName name="Motorcycle">#REF!</definedName>
+    <definedName name="MotorVehicles">#REF!</definedName>
+    <definedName name="OfficeEquipment">#REF!</definedName>
+    <definedName name="OtheMedicalEquipment">#REF!</definedName>
+    <definedName name="OtherCommunication\TelecommunicationFacilities">#REF!</definedName>
+    <definedName name="OtherCommunicationEquipment">#REF!</definedName>
+    <definedName name="OtherDisasterResponseandRescue">#REF!</definedName>
+    <definedName name="OtherFloodControlSystemFacilities">#REF!</definedName>
+    <definedName name="OtherFurnitureFixturesandBooks">#REF!</definedName>
+    <definedName name="OtherICTEquipment">#REF!</definedName>
+    <definedName name="OtherInfrastructureAssets\Components">#REF!</definedName>
+    <definedName name="OtherMachineryEquipment">#REF!</definedName>
+    <definedName name="OtherOfficeEquipment">#REF!</definedName>
+    <definedName name="OtherPoliceandSecurityEquipment">#REF!</definedName>
+    <definedName name="OtherRoadNetworkFacilities">#REF!</definedName>
+    <definedName name="OtherStructures">#REF!</definedName>
+    <definedName name="OtherTransportationEquipment">#REF!</definedName>
+    <definedName name="Parks\Plazas\Monuments">#REF!</definedName>
+    <definedName name="PeripheralsandAuxiliaryEquipmentnecessarytoputthesystemintooperationalmode">#REF!</definedName>
+    <definedName name="PoliceandSecurityEquipment">#REF!</definedName>
+    <definedName name="PoliceEquipment">#REF!</definedName>
+    <definedName name="PreLoadedSoftwareOperatingSystemsincludedinthecostofthecomputerhardware">#REF!</definedName>
+    <definedName name="Printers">#REF!</definedName>
+    <definedName name="Radio">#REF!</definedName>
+    <definedName name="RiverWalls">#REF!</definedName>
+    <definedName name="RoadNetworks">#REF!</definedName>
+    <definedName name="Roads">#REF!</definedName>
+    <definedName name="Scanners">#REF!</definedName>
+    <definedName name="SchoolBuildings">#REF!</definedName>
+    <definedName name="Seawalls">#REF!</definedName>
+    <definedName name="SecurityCameras">#REF!</definedName>
+    <definedName name="Slaughterhouses">#REF!</definedName>
+    <definedName name="SpecializedEquipments">#REF!</definedName>
+    <definedName name="SurveyEquipments">#REF!</definedName>
+    <definedName name="TechnicalandScientificEquipment">#REF!</definedName>
+    <definedName name="TherapeuticEquipment">#REF!</definedName>
+    <definedName name="Towers">#REF!</definedName>
+    <definedName name="Transceivers">#REF!</definedName>
+    <definedName name="Transmitters">#REF!</definedName>
+    <definedName name="Truck">#REF!</definedName>
+    <definedName name="VolcanicEruptionRescueEquipment">#REF!</definedName>
+    <definedName name="WasteTreatmentPlants">#REF!</definedName>
+    <definedName name="Watercrafts">#REF!</definedName>
+    <definedName name="WaterSourceFacility">#REF!</definedName>
+    <definedName name="WaterSupplySystems">#REF!</definedName>
+    <definedName name="WaterTreatmentPlants">#REF!</definedName>
+    <definedName name="WeekdayOption">MATCH(WeekStart,Weekdays,0)+10</definedName>
+    <definedName name="Weekdays">{"Monday","Tuesday","Wednesday","Thursday","Friday","Saturday","Sunday"}</definedName>
+    <definedName name="WeekStart">#REF!</definedName>
+    <definedName name="WeekStartValue">IF(WeekStart="Monday",2,1)</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,6 +181,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
+    <t>REPORT ON THE PHYSICAL COUNT OF EQUIPMENT</t>
+  </si>
+  <si>
     <t>Custodian 
 Item 
 Number</t>
@@ -152,6 +300,9 @@
   <si>
     <t>Sub-
 Location</t>
+  </si>
+  <si>
+    <t>Number</t>
   </si>
   <si>
     <t>Accountable 
@@ -181,13 +332,10 @@
 Number</t>
   </si>
   <si>
-    <t>Department:</t>
+    <t>Specifications</t>
   </si>
   <si>
     <t>Annex</t>
-  </si>
-  <si>
-    <t>REPORT ON THE PHYSICAL COUNT OF EQUIPMENT</t>
   </si>
   <si>
     <t>Old
@@ -195,23 +343,36 @@
 (in RPCPPE)</t>
   </si>
   <si>
-    <t>Specifications</t>
-  </si>
-  <si>
-    <t>PAR / ICS / ARE / MR / RPCPPE</t>
-  </si>
-  <si>
-    <t>S</t>
+    <t>PAR / ICS / ARE / MR /RPCPPE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Department:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -253,13 +414,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -393,21 +555,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -432,13 +579,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -447,9 +592,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -462,14 +618,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -477,65 +630,75 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -545,30 +708,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -582,6 +723,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -881,378 +1026,340 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8360D46A-3DF6-4255-A30F-B9008CB83C98}">
-  <dimension ref="B2:AN15"/>
+  <dimension ref="B1:AN14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="3"/>
-    <col min="6" max="6" width="28.44140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="3"/>
-    <col min="8" max="8" width="11.77734375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="28" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="42.33203125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" style="17"/>
-    <col min="14" max="14" width="8.88671875" style="3"/>
-    <col min="15" max="16" width="16.5546875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="10.21875" style="13" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="3"/>
-    <col min="21" max="21" width="12.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" style="13" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" style="13" customWidth="1"/>
-    <col min="24" max="24" width="11.21875" style="13" customWidth="1"/>
-    <col min="25" max="25" width="10.77734375" style="3" customWidth="1"/>
-    <col min="26" max="27" width="8.88671875" style="3"/>
-    <col min="28" max="28" width="11.5546875" style="13" customWidth="1"/>
-    <col min="29" max="29" width="12.44140625" style="3" customWidth="1"/>
-    <col min="30" max="32" width="8.88671875" style="3"/>
-    <col min="33" max="33" width="22.88671875" style="3" customWidth="1"/>
-    <col min="34" max="34" width="25.21875" style="3" customWidth="1"/>
-    <col min="35" max="35" width="25.33203125" style="3" customWidth="1"/>
-    <col min="36" max="36" width="26.33203125" style="3" customWidth="1"/>
-    <col min="37" max="37" width="6.5546875" style="3" customWidth="1"/>
-    <col min="38" max="38" width="17.77734375" style="3" customWidth="1"/>
-    <col min="39" max="39" width="18" style="3" customWidth="1"/>
-    <col min="40" max="40" width="6.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="2.77734375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="5"/>
+    <col min="6" max="6" width="35.44140625" style="14" customWidth="1"/>
+    <col min="7" max="9" width="8.88671875" style="14"/>
+    <col min="10" max="10" width="23.33203125" style="14" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="14"/>
+    <col min="12" max="12" width="12.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="8.88671875" style="14"/>
+    <col min="17" max="17" width="10.21875" style="6" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" style="14" customWidth="1"/>
+    <col min="19" max="19" width="8.88671875" style="5"/>
+    <col min="20" max="20" width="8.88671875" style="14"/>
+    <col min="21" max="21" width="12.44140625" style="5" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="6"/>
+    <col min="23" max="23" width="19.5546875" style="6" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" style="6" customWidth="1"/>
+    <col min="25" max="25" width="10.6640625" style="14" customWidth="1"/>
+    <col min="26" max="27" width="8.88671875" style="5"/>
+    <col min="28" max="28" width="8.88671875" style="6"/>
+    <col min="29" max="29" width="8.88671875" style="14"/>
+    <col min="30" max="30" width="8.88671875" style="5"/>
+    <col min="31" max="32" width="8.88671875" style="14"/>
+    <col min="33" max="33" width="8.88671875" style="5"/>
+    <col min="34" max="34" width="12.77734375" style="14" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" style="14"/>
+    <col min="36" max="36" width="18.109375" style="14" customWidth="1"/>
+    <col min="37" max="37" width="8.88671875" style="5"/>
+    <col min="38" max="38" width="8.88671875" style="14"/>
+    <col min="39" max="39" width="29.5546875" style="14" customWidth="1"/>
+    <col min="40" max="40" width="8.88671875" style="14"/>
+    <col min="41" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:40" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:40" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:40" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
-      <c r="M2" s="15"/>
-      <c r="Q2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="AB2" s="11"/>
     </row>
-    <row r="3" spans="2:40" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="B3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="16"/>
-      <c r="Q3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="AB3" s="12"/>
+    <row r="3" spans="2:40" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+    <row r="4" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B4" s="10"/>
+      <c r="T4" s="8"/>
+      <c r="V4" s="8"/>
     </row>
-    <row r="5" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
+    <row r="5" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="10"/>
     </row>
-    <row r="6" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
+    <row r="6" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="11"/>
     </row>
-    <row r="7" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="1"/>
+    <row r="7" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
     </row>
-    <row r="8" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="15"/>
+    </row>
+    <row r="9" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="11"/>
+    </row>
+    <row r="11" spans="2:40" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="12"/>
+    </row>
+    <row r="12" spans="2:40" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH12" s="19"/>
+      <c r="AI12" s="19"/>
+      <c r="AJ12" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="9"/>
+      <c r="AK12" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN12" s="16" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="9" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="1"/>
-      <c r="C9" s="9"/>
-    </row>
-    <row r="10" spans="2:40" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="2:40" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="24" t="s">
+    <row r="13" spans="2:40" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="28"/>
+      <c r="C13" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="24" t="s">
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="R12" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="S12" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="U12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="V12" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="W12" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="X12" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y12" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z12" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA12" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB12" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC12" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD12" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE12" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF12" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="AG12" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH12" s="21"/>
-      <c r="AI12" s="21"/>
-      <c r="AJ12" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK12" s="21" t="s">
+      <c r="L13" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH13" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="AL12" s="21" t="s">
+      <c r="AI13" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="AM12" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="AN12" s="21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="2:40" s="4" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="32"/>
-      <c r="C13" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="36"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="26"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="26"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH13" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI13" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ13" s="22"/>
+      <c r="AJ13" s="20"/>
       <c r="AK13" s="22"/>
       <c r="AL13" s="22"/>
-      <c r="AM13" s="39"/>
-      <c r="AN13" s="22"/>
+      <c r="AM13" s="22"/>
+      <c r="AN13" s="17"/>
     </row>
-    <row r="14" spans="2:40" s="4" customFormat="1" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="33"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
+    <row r="14" spans="2:40" s="2" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="29"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="23"/>
       <c r="H14" s="23"/>
       <c r="I14" s="23"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="N14" s="6" t="s">
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="27"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
+      <c r="N14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
       <c r="AG14" s="23"/>
-      <c r="AH14" s="23"/>
-      <c r="AI14" s="23"/>
-      <c r="AJ14" s="23"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
       <c r="AK14" s="23"/>
       <c r="AL14" s="23"/>
-      <c r="AM14" s="40"/>
-      <c r="AN14" s="23"/>
-    </row>
-    <row r="15" spans="2:40" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="19"/>
-      <c r="Q15" s="20"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="14"/>
-      <c r="AB15" s="14"/>
+      <c r="AM14" s="23"/>
+      <c r="AN14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="40">
     <mergeCell ref="O12:O14"/>
-    <mergeCell ref="AG13:AG14"/>
     <mergeCell ref="P12:P14"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="AN12:AN14"/>
+    <mergeCell ref="AB12:AB14"/>
+    <mergeCell ref="T12:T14"/>
+    <mergeCell ref="V12:V14"/>
+    <mergeCell ref="Q12:Q14"/>
+    <mergeCell ref="W12:W14"/>
+    <mergeCell ref="X12:X14"/>
+    <mergeCell ref="Y12:Y14"/>
+    <mergeCell ref="Z12:Z14"/>
+    <mergeCell ref="AA12:AA14"/>
+    <mergeCell ref="S12:S14"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="G12:N12"/>
     <mergeCell ref="G13:G14"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="K13:K14"/>
-    <mergeCell ref="Y12:Y14"/>
-    <mergeCell ref="Z12:Z14"/>
-    <mergeCell ref="S12:S14"/>
-    <mergeCell ref="T12:T14"/>
-    <mergeCell ref="Q12:Q14"/>
-    <mergeCell ref="AM12:AM14"/>
-    <mergeCell ref="AJ12:AJ14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="AL12:AL14"/>
-    <mergeCell ref="R12:R14"/>
-    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="AN12:AN14"/>
     <mergeCell ref="AD12:AD14"/>
     <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="U12:U14"/>
     <mergeCell ref="AF12:AF14"/>
-    <mergeCell ref="AA12:AA14"/>
-    <mergeCell ref="AB12:AB14"/>
-    <mergeCell ref="U12:U14"/>
-    <mergeCell ref="V12:V14"/>
-    <mergeCell ref="W12:W14"/>
-    <mergeCell ref="X12:X14"/>
-    <mergeCell ref="AK12:AK14"/>
+    <mergeCell ref="AC12:AC14"/>
+    <mergeCell ref="AL12:AL14"/>
+    <mergeCell ref="AM12:AM14"/>
+    <mergeCell ref="AG13:AG14"/>
     <mergeCell ref="AH13:AH14"/>
     <mergeCell ref="AI13:AI14"/>
     <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AJ12:AJ14"/>
+    <mergeCell ref="AK12:AK14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFE98289BC91294F829EFFD4DC549C76" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="19972903a613892b44bc7de177b9930c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="24f70235-d7ab-48ae-872a-f5e45d821dca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="851bba6bbcd0ff4aaccc95eb8de2c74d" ns3:_="">
     <xsd:import namespace="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
@@ -1402,7 +1509,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1411,23 +1518,13 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E727EF53-D248-4693-8734-5FECE57054A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1445,10 +1542,26 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{961ECCB7-21B8-4C05-838A-3ADAC8FDED02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D6BA337-C593-4EF2-B090-937D907018AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="24f70235-d7ab-48ae-872a-f5e45d821dca"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
+++ b/iLgs/App_Data/CustodianEquipmentTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Template  2025_04_22/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3cb8fbe057445bdd/Documents/LPC/GSO/Tempalte 2025_06_24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{148159D7-4E6E-4289-9B74-FEF0EA63799C}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{4CCB3B42-D639-4A82-BB32-781160A643F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38F873B-E9F3-4F6B-871E-B197F1AD71DA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="986" xr2:uid="{8F9EB15D-4C1E-42CC-8141-A131BDAE685A}"/>
   </bookViews>
@@ -373,7 +373,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,6 +431,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -618,10 +628,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -666,6 +677,22 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -708,8 +735,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1038,19 +1081,21 @@
     <col min="7" max="9" width="8.88671875" style="14"/>
     <col min="10" max="10" width="23.33203125" style="14" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" style="14"/>
-    <col min="12" max="12" width="12.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="8.88671875" style="14"/>
-    <col min="17" max="17" width="10.21875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="39.33203125" style="14" customWidth="1"/>
+    <col min="13" max="14" width="8.88671875" style="14"/>
+    <col min="15" max="16" width="14.44140625" style="14" customWidth="1"/>
+    <col min="17" max="17" width="10.21875" style="20" customWidth="1"/>
     <col min="18" max="18" width="11.5546875" style="14" customWidth="1"/>
     <col min="19" max="19" width="8.88671875" style="5"/>
     <col min="20" max="20" width="8.88671875" style="14"/>
     <col min="21" max="21" width="12.44140625" style="5" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="6"/>
-    <col min="23" max="23" width="19.5546875" style="6" customWidth="1"/>
-    <col min="24" max="24" width="11.33203125" style="6" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="20"/>
+    <col min="23" max="23" width="19.5546875" style="20" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" style="20" customWidth="1"/>
     <col min="25" max="25" width="10.6640625" style="14" customWidth="1"/>
-    <col min="26" max="27" width="8.88671875" style="5"/>
-    <col min="28" max="28" width="8.88671875" style="6"/>
+    <col min="26" max="26" width="8.88671875" style="21"/>
+    <col min="27" max="27" width="8.88671875" style="5"/>
+    <col min="28" max="28" width="8.88671875" style="20"/>
     <col min="29" max="29" width="8.88671875" style="14"/>
     <col min="30" max="30" width="8.88671875" style="5"/>
     <col min="31" max="32" width="8.88671875" style="14"/>
@@ -1060,222 +1105,288 @@
     <col min="36" max="36" width="18.109375" style="14" customWidth="1"/>
     <col min="37" max="37" width="8.88671875" style="5"/>
     <col min="38" max="38" width="8.88671875" style="14"/>
-    <col min="39" max="39" width="29.5546875" style="14" customWidth="1"/>
+    <col min="39" max="39" width="38.44140625" style="14" customWidth="1"/>
     <col min="40" max="40" width="8.88671875" style="14"/>
     <col min="41" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:40" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AB1" s="16"/>
+    </row>
     <row r="2" spans="2:40" s="8" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="7"/>
+      <c r="Q2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Z2" s="17"/>
+      <c r="AB2" s="17"/>
     </row>
     <row r="3" spans="2:40" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
+      <c r="Q3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Z3" s="18"/>
+      <c r="AB3" s="18"/>
     </row>
     <row r="4" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="10"/>
+      <c r="Q4" s="19"/>
       <c r="T4" s="8"/>
-      <c r="V4" s="8"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AB4" s="19"/>
     </row>
     <row r="5" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="10"/>
+      <c r="Q5" s="19"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Z5" s="19"/>
+      <c r="AB5" s="19"/>
     </row>
     <row r="6" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="11"/>
+      <c r="Q6" s="19"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AB6" s="19"/>
     </row>
     <row r="7" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="11"/>
+      <c r="Q7" s="19"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AB7" s="19"/>
     </row>
     <row r="8" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="15"/>
+      <c r="Q8" s="19"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AB8" s="19"/>
     </row>
     <row r="9" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
+      <c r="Q9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AB9" s="19"/>
     </row>
     <row r="10" spans="2:40" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="11"/>
+      <c r="Q10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AB10" s="19"/>
     </row>
     <row r="11" spans="2:40" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="12"/>
+      <c r="Q11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AB11" s="19"/>
     </row>
     <row r="12" spans="2:40" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19" t="s">
+      <c r="D12" s="25"/>
+      <c r="E12" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19" t="s">
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="19" t="s">
+      <c r="P12" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="Q12" s="19" t="s">
+      <c r="Q12" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="R12" s="19" t="s">
+      <c r="R12" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="S12" s="19" t="s">
+      <c r="S12" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="T12" s="19" t="s">
+      <c r="T12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="U12" s="19" t="s">
+      <c r="U12" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="V12" s="19" t="s">
+      <c r="V12" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="W12" s="19" t="s">
+      <c r="W12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="X12" s="19" t="s">
+      <c r="X12" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="Y12" s="19" t="s">
+      <c r="Y12" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="Z12" s="19" t="s">
+      <c r="Z12" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="AA12" s="19" t="s">
+      <c r="AA12" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="AB12" s="19" t="s">
+      <c r="AB12" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="AC12" s="19" t="s">
+      <c r="AC12" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="AD12" s="19" t="s">
+      <c r="AD12" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="AE12" s="19" t="s">
+      <c r="AE12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="AF12" s="19" t="s">
+      <c r="AF12" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="AG12" s="19" t="s">
+      <c r="AG12" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="19" t="s">
+      <c r="AH12" s="25"/>
+      <c r="AI12" s="25"/>
+      <c r="AJ12" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="AK12" s="19" t="s">
+      <c r="AK12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="AL12" s="19" t="s">
+      <c r="AL12" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="AM12" s="19" t="s">
+      <c r="AM12" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="AN12" s="16" t="s">
+      <c r="AN12" s="22" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="2:40" s="2" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="28"/>
-      <c r="C13" s="22" t="s">
+      <c r="B13" s="34"/>
+      <c r="C13" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="22" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="24" t="s">
+      <c r="L13" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="25"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="20"/>
-      <c r="AC13" s="20"/>
-      <c r="AD13" s="20"/>
-      <c r="AE13" s="20"/>
-      <c r="AF13" s="20"/>
-      <c r="AG13" s="22" t="s">
+      <c r="M13" s="31"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="37"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="37"/>
+      <c r="AC13" s="26"/>
+      <c r="AD13" s="26"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="AH13" s="22" t="s">
+      <c r="AH13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="AI13" s="22" t="s">
+      <c r="AI13" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="AJ13" s="20"/>
-      <c r="AK13" s="22"/>
-      <c r="AL13" s="22"/>
-      <c r="AM13" s="22"/>
-      <c r="AN13" s="17"/>
+      <c r="AJ13" s="26"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="28"/>
+      <c r="AM13" s="28"/>
+      <c r="AN13" s="23"/>
     </row>
     <row r="14" spans="2:40" s="2" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="29"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
       <c r="L14" s="3" t="s">
         <v>40</v>
       </c>
@@ -1285,32 +1396,32 @@
       <c r="N14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="23"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
-      <c r="AK14" s="23"/>
-      <c r="AL14" s="23"/>
-      <c r="AM14" s="23"/>
-      <c r="AN14" s="18"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="27"/>
+      <c r="AE14" s="27"/>
+      <c r="AF14" s="27"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="27"/>
+      <c r="AI14" s="27"/>
+      <c r="AJ14" s="27"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="29"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="40">
